--- a/slide_classification/TCGA_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -758,13 +758,13 @@
         <v>0.845360824742268</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8482142857142857</v>
+        <v>0.8392857142857143</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8613861386138614</v>
+        <v>0.8910891089108911</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8523325452773125</v>
+        <v>0.857526144994427</v>
       </c>
     </row>
     <row r="15">
@@ -780,13 +780,13 @@
         <v>0.5206043956043956</v>
       </c>
       <c r="D15" t="n">
-        <v>0.633695652173913</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5608614232209738</v>
+        <v>0.5777153558052435</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5952676404770934</v>
+        <v>0.5932311236231608</v>
       </c>
     </row>
     <row r="16">
@@ -802,13 +802,13 @@
         <v>0.5164506480558325</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6633068081343944</v>
+        <v>0.6326530612244898</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5730676328502415</v>
+        <v>0.6039215686274509</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6082869674804772</v>
+        <v>0.6083370146973034</v>
       </c>
     </row>
     <row r="17">
@@ -824,13 +824,13 @@
         <v>0.808358429865044</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8237084754326134</v>
+        <v>0.8097667638483965</v>
       </c>
       <c r="E17" t="n">
-        <v>0.840543836992395</v>
+        <v>0.8610366919044846</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8300273578800106</v>
+        <v>0.831665143711979</v>
       </c>
     </row>
     <row r="18">
@@ -846,13 +846,13 @@
         <v>0.5425824175824175</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6391304347826088</v>
+        <v>0.6029891304347825</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5608614232209737</v>
+        <v>0.5805243445692884</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6035412961692272</v>
+        <v>0.5994217004193494</v>
       </c>
     </row>
     <row r="19">
@@ -873,17 +873,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[89, 3], [14, 6]]</t>
+          <t>[[89, 3], [15, 5]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[85, 4], [10, 2]]</t>
+          <t>[[88, 1], [10, 2]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[84, 4], [11, 4]]</t>
+          <t>[[85, 3], [12, 4]]</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1406,38 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8523325452773125</v>
+        <v>0.857526144994427</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006157908987499901</v>
+        <v>0.0201068947738193</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5952676404770934</v>
+        <v>0.5932311236231608</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05750068374137605</v>
+        <v>0.05252765758579703</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6082869674804772</v>
+        <v>0.6083370146973034</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06687797166328885</v>
+        <v>0.05965698029232639</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8300273578800106</v>
+        <v>0.831665143711979</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01520949102340242</v>
+        <v>0.02310914839348416</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6035412961692272</v>
+        <v>0.5994217004193494</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05346702965256648</v>
+        <v>0.04692796439420401</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[[84, 4], [11, 4]]</t>
+          <t>[[85, 3], [12, 4]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -616,13 +616,13 @@
         <v>0.8144329896907216</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7946428571428571</v>
       </c>
       <c r="E8" t="n">
         <v>0.801980198019802</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7801435188416392</v>
+        <v>0.782375661698782</v>
       </c>
     </row>
     <row r="9">
@@ -635,16 +635,16 @@
         <v>0.696969696969697</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7953296703296704</v>
+        <v>0.7303113553113554</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7521739130434782</v>
+        <v>0.7576086956521739</v>
       </c>
       <c r="E9" t="n">
         <v>0.6713483146067416</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7289553987373968</v>
+        <v>0.714059515634992</v>
       </c>
     </row>
     <row r="10">
@@ -657,16 +657,16 @@
         <v>0.6117249447549721</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7054655870445343</v>
+        <v>0.6790441176470587</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6994633273703041</v>
+        <v>0.7080358154822624</v>
       </c>
       <c r="E10" t="n">
         <v>0.6286764705882353</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6613325824395115</v>
+        <v>0.6568703371181321</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         <v>0.755996814655613</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8365958512458783</v>
+        <v>0.8316252274105518</v>
       </c>
       <c r="D11" t="n">
-        <v>0.802964477383082</v>
+        <v>0.8102605203931283</v>
       </c>
       <c r="E11" t="n">
         <v>0.8220733838089691</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8044076317733856</v>
+        <v>0.8049889865670656</v>
       </c>
     </row>
     <row r="12">
@@ -701,16 +701,16 @@
         <v>0.8613636363636364</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8516483516483516</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8608695652173913</v>
+        <v>0.8679347826086956</v>
       </c>
       <c r="E12" t="n">
         <v>0.7443820224719101</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8295658939253223</v>
+        <v>0.8327058246467748</v>
       </c>
     </row>
     <row r="13">
@@ -726,12 +726,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[69, 15], [3, 10]]</t>
+          <t>[[71, 13], [5, 8]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[74, 18], [6, 14]]</t>
+          <t>[[75, 17], [6, 14]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[70, 18], [5, 10]]</t>
+          <t>[[71, 17], [6, 10]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7801435188416392</v>
+        <v>0.782375661698782</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03704777782520023</v>
+        <v>0.03758130814589417</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7289553987373968</v>
+        <v>0.714059515634992</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04818273704241807</v>
+        <v>0.03269924298941575</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6613325824395115</v>
+        <v>0.6568703371181321</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04162035308093785</v>
+        <v>0.03854407633056146</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8044076317733856</v>
+        <v>0.8049889865670656</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03038852652069841</v>
+        <v>0.02928048809733204</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8295658939253223</v>
+        <v>0.8327058246467748</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0493329077680814</v>
+        <v>0.05113856724459803</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[70, 18], [5, 10]]</t>
+          <t>[[71, 17], [6, 10]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -474,13 +474,13 @@
         <v>0.8762886597938144</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8660714285714286</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9108910891089109</v>
+        <v>0.900990099009901</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8866137652423249</v>
+        <v>0.8819063748604296</v>
       </c>
     </row>
     <row r="3">
@@ -493,16 +493,16 @@
         <v>0.7992424242424242</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6359890109890109</v>
+        <v>0.6684981684981685</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7228260869565217</v>
+        <v>0.6978260869565217</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7331460674157304</v>
+        <v>0.6914794007490637</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7228008974009219</v>
+        <v>0.7142615201115445</v>
       </c>
     </row>
     <row r="4">
@@ -515,16 +515,16 @@
         <v>0.7911520737327189</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6655172413793103</v>
+        <v>0.6923890063424947</v>
       </c>
       <c r="D4" t="n">
-        <v>0.746031746031746</v>
+        <v>0.7226006191950465</v>
       </c>
       <c r="E4" t="n">
-        <v>0.760852407261247</v>
+        <v>0.7225274725274725</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7408883671012556</v>
+        <v>0.7321672929494332</v>
       </c>
     </row>
     <row r="5">
@@ -537,16 +537,16 @@
         <v>0.8946212697418461</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8598649129043726</v>
+        <v>0.8664806782764106</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8582766439909297</v>
+        <v>0.8467934542237947</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9052646385396235</v>
+        <v>0.8921771298008921</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8795068662941929</v>
+        <v>0.8750181330107358</v>
       </c>
     </row>
     <row r="6">
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9196969696969698</v>
+        <v>0.921969696969697</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8076923076923078</v>
+        <v>0.8278388278388279</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8548913043478261</v>
+        <v>0.8581521739130434</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7734082397003745</v>
+        <v>0.7911985018726592</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8389222053593696</v>
+        <v>0.8497898001485569</v>
       </c>
     </row>
     <row r="7">
@@ -584,22 +584,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[[81, 3], [9, 4]]</t>
+          <t>[[80, 4], [8, 5]]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[[87, 5], [10, 10]]</t>
+          <t>[[87, 5], [11, 9]]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[[86, 3], [6, 6]]</t>
+          <t>[[86, 3], [7, 5]]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[[84, 4], [8, 8]]</t>
+          <t>[[84, 4], [8, 7]]</t>
         </is>
       </c>
     </row>
@@ -610,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7184466019417476</v>
+        <v>0.7864077669902912</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8144329896907216</v>
+        <v>0.8350515463917526</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7946428571428571</v>
+        <v>0.7678571428571429</v>
       </c>
       <c r="E8" t="n">
-        <v>0.801980198019802</v>
+        <v>0.8316831683168316</v>
       </c>
       <c r="F8" t="n">
-        <v>0.782375661698782</v>
+        <v>0.8052499061390046</v>
       </c>
     </row>
     <row r="9">
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.696969696969697</v>
+        <v>0.7920454545454545</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7303113553113554</v>
+        <v>0.7097069597069596</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7576086956521739</v>
+        <v>0.741304347826087</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6713483146067416</v>
+        <v>0.724250936329588</v>
       </c>
       <c r="F9" t="n">
-        <v>0.714059515634992</v>
+        <v>0.7418269246020223</v>
       </c>
     </row>
     <row r="10">
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6117249447549721</v>
+        <v>0.6921195652173913</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6790441176470587</v>
+        <v>0.6845528455284553</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7080358154822624</v>
+        <v>0.6827886710239651</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6286764705882353</v>
+        <v>0.6760988492737219</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6568703371181321</v>
+        <v>0.6838899827608833</v>
       </c>
     </row>
     <row r="11">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.755996814655613</v>
+        <v>0.8128746306458421</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8316252274105518</v>
+        <v>0.8440365434582181</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8102605203931283</v>
+        <v>0.7883909119203236</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8220733838089691</v>
+        <v>0.8472416002211426</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8049889865670656</v>
+        <v>0.8231359215613816</v>
       </c>
     </row>
     <row r="12">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8613636363636364</v>
+        <v>0.8560606060606062</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8232600732600733</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8679347826086956</v>
+        <v>0.8576086956521739</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7443820224719101</v>
+        <v>0.8342696629213484</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8327058246467748</v>
+        <v>0.8427997594735505</v>
       </c>
     </row>
     <row r="13">
@@ -721,27 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[64, 24], [5, 10]]</t>
+          <t>[[69, 19], [3, 12]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[71, 13], [5, 8]]</t>
+          <t>[[74, 10], [6, 7]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[75, 17], [6, 14]]</t>
+          <t>[[72, 20], [6, 14]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[75, 14], [6, 6]]</t>
+          <t>[[77, 12], [5, 7]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[71, 17], [6, 10]]</t>
+          <t>[[73, 15], [5, 10]]</t>
         </is>
       </c>
     </row>
@@ -755,16 +755,16 @@
         <v>0.8543689320388349</v>
       </c>
       <c r="C14" t="n">
-        <v>0.845360824742268</v>
+        <v>0.865979381443299</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392857142857143</v>
+        <v>0.8303571428571429</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8910891089108911</v>
+        <v>0.900990099009901</v>
       </c>
       <c r="F14" t="n">
-        <v>0.857526144994427</v>
+        <v>0.8629238888372944</v>
       </c>
     </row>
     <row r="15">
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6659090909090909</v>
+        <v>0.6382575757575758</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5206043956043956</v>
+        <v>0.5325091575091575</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.5836956521739131</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5777153558052435</v>
+        <v>0.6193820224719101</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5932311236231608</v>
+        <v>0.5934611019781391</v>
       </c>
     </row>
     <row r="16">
@@ -796,19 +796,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.68032278088144</v>
+        <v>0.6585635359116022</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5164506480558325</v>
+        <v>0.5303538175046555</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6326530612244898</v>
+        <v>0.5999247978943411</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6039215686274509</v>
+        <v>0.6606182795698925</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6083370146973034</v>
+        <v>0.6123651077201228</v>
       </c>
     </row>
     <row r="17">
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8474986892299905</v>
+        <v>0.8418173040819611</v>
       </c>
       <c r="C17" t="n">
-        <v>0.808358429865044</v>
+        <v>0.8209564399393345</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8097667638483965</v>
+        <v>0.7951145489216556</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8610366919044846</v>
+        <v>0.8783668689449591</v>
       </c>
       <c r="F17" t="n">
-        <v>0.831665143711979</v>
+        <v>0.8340637904719777</v>
       </c>
     </row>
     <row r="18">
@@ -840,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6715909090909091</v>
+        <v>0.6492424242424242</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5425824175824175</v>
+        <v>0.6126373626373627</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6029891304347825</v>
+        <v>0.6051630434782609</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5805243445692884</v>
+        <v>0.6264044943820226</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5994217004193494</v>
+        <v>0.6233618311850175</v>
       </c>
     </row>
     <row r="19">
@@ -863,27 +863,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[82, 6], [9, 6]]</t>
+          <t>[[83, 5], [10, 5]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[81, 3], [12, 1]]</t>
+          <t>[[83, 1], [12, 1]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[89, 3], [15, 5]]</t>
+          <t>[[89, 3], [16, 4]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[88, 1], [10, 2]]</t>
+          <t>[[88, 1], [9, 3]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[85, 3], [12, 4]]</t>
+          <t>[[86, 2], [12, 3]]</t>
         </is>
       </c>
     </row>
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6504854368932039</v>
+        <v>0.6407766990291263</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4742268041237113</v>
+        <v>0.4948453608247423</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6160714285714286</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7920792079207921</v>
+        <v>0.7821782178217822</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6399121479487127</v>
+        <v>0.6334679265617699</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6848484848484848</v>
+        <v>0.6791666666666667</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4688644688644689</v>
+        <v>0.4807692307692308</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5673913043478261</v>
+        <v>0.5315217391304348</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7378277153558053</v>
+        <v>0.7322097378277153</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6147329933541463</v>
+        <v>0.6059168435985118</v>
       </c>
     </row>
     <row r="22">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5680335507921714</v>
+        <v>0.5605903378300473</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4005816066884769</v>
+        <v>0.4141501294219154</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5346904860822601</v>
+        <v>0.5052901900359528</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6525798525798525</v>
+        <v>0.6434531450577663</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5389713740356903</v>
+        <v>0.5308709505864204</v>
       </c>
     </row>
     <row r="23">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7017888326894018</v>
+        <v>0.6936268007285191</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5543701072149958</v>
+        <v>0.5732990580219349</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6789126951154371</v>
+        <v>0.6557854574803726</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8204150144744204</v>
+        <v>0.8130060117693413</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6888716623735638</v>
+        <v>0.6839293320000419</v>
       </c>
     </row>
     <row r="24">
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7818181818181819</v>
+        <v>0.781060606060606</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4853479853479853</v>
+        <v>0.5155677655677655</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6489130434782608</v>
+        <v>0.6652173913043478</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8192883895131086</v>
+        <v>0.8286516853932584</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6838419000393842</v>
+        <v>0.6976243620814944</v>
       </c>
     </row>
     <row r="25">
@@ -1005,27 +1005,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[[56, 32], [4, 11]]</t>
+          <t>[[55, 33], [4, 11]]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[[40, 44], [7, 6]]</t>
+          <t>[[42, 42], [7, 6]]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[[63, 29], [11, 9]]</t>
+          <t>[[61, 31], [12, 8]]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[[72, 17], [4, 8]]</t>
+          <t>[[71, 18], [4, 8]]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[[58, 30], [6, 8]]</t>
+          <t>[[57, 31], [7, 8]]</t>
         </is>
       </c>
     </row>
@@ -1036,19 +1036,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.912621359223301</v>
+        <v>0.9223300970873787</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8762886597938144</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8482142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E26" t="n">
         <v>0.900990099009901</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8845286009353255</v>
+        <v>0.8917652478461167</v>
       </c>
     </row>
     <row r="27">
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7276515151515152</v>
+        <v>0.7609848484848485</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5709706959706959</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="D27" t="n">
-        <v>0.575</v>
+        <v>0.6</v>
       </c>
       <c r="E27" t="n">
         <v>0.6193820224719101</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6232510583985303</v>
+        <v>0.6393224869699589</v>
       </c>
     </row>
     <row r="28">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7797576621525303</v>
+        <v>0.8113553113553114</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5912921348314606</v>
+        <v>0.6026070763500931</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5881462253947654</v>
+        <v>0.6266666666666667</v>
       </c>
       <c r="E28" t="n">
         <v>0.6606182795698925</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6549535754871623</v>
+        <v>0.675311833485491</v>
       </c>
     </row>
     <row r="29">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9009957857296086</v>
+        <v>0.9139016323482343</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8411039036256226</v>
+        <v>0.8485016030255909</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7985383640802201</v>
+        <v>0.8152380952380953</v>
       </c>
       <c r="E29" t="n">
         <v>0.8783668689449591</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8547512305951026</v>
+        <v>0.86400204988922</v>
       </c>
     </row>
     <row r="30">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9318181818181818</v>
+        <v>0.9583333333333333</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7445054945054945</v>
+        <v>0.7600732600732601</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7603260869565218</v>
+        <v>0.7951086956521739</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8122659176029963</v>
+        <v>0.7911985018726593</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8122289202207986</v>
+        <v>0.8261784477328566</v>
       </c>
     </row>
     <row r="31">
@@ -1147,17 +1147,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[[87, 1], [8, 7]]</t>
+          <t>[[87, 1], [7, 8]]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[[83, 1], [11, 2]]</t>
+          <t>[[84, 0], [11, 2]]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[[92, 0], [17, 3]]</t>
+          <t>[[92, 0], [16, 4]]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[[88, 1], [11, 4]]</t>
+          <t>[[88, 0], [11, 4]]</t>
         </is>
       </c>
     </row>
@@ -1290,38 +1290,38 @@
         <v>413</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8866137652423249</v>
+        <v>0.8819063748604296</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01703975873606035</v>
+        <v>0.01685684401869761</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7228008974009219</v>
+        <v>0.7142615201115445</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05806598364232635</v>
+        <v>0.05026227920476448</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7408883671012556</v>
+        <v>0.7321672929494332</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04645498908421853</v>
+        <v>0.03621451309187567</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8795068662941929</v>
+        <v>0.8750181330107358</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0207872358350007</v>
+        <v>0.0196738072478985</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8389222053593696</v>
+        <v>0.8497898001485569</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05487932415983524</v>
+        <v>0.04794437458942683</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[[84, 4], [8, 8]]</t>
+          <t>[[84, 4], [8, 7]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.782375661698782</v>
+        <v>0.8052499061390046</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03758130814589417</v>
+        <v>0.02889679941043978</v>
       </c>
       <c r="H3" t="n">
-        <v>0.714059515634992</v>
+        <v>0.7418269246020223</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03269924298941575</v>
+        <v>0.03107563895070763</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6568703371181321</v>
+        <v>0.6838899827608833</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03854407633056146</v>
+        <v>0.005702632352995822</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8049889865670656</v>
+        <v>0.8231359215613816</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02928048809733204</v>
+        <v>0.02413726126517217</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8327058246467748</v>
+        <v>0.8427997594735505</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05113856724459803</v>
+        <v>0.01457494877743149</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[71, 17], [6, 10]]</t>
+          <t>[[73, 15], [5, 10]]</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1406,38 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.857526144994427</v>
+        <v>0.8629238888372944</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0201068947738193</v>
+        <v>0.02545659355417389</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5932311236231608</v>
+        <v>0.5934611019781391</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05252765758579703</v>
+        <v>0.04027754252292719</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6083370146973034</v>
+        <v>0.6123651077201228</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05965698029232639</v>
+        <v>0.05325240931707628</v>
       </c>
       <c r="L4" t="n">
-        <v>0.831665143711979</v>
+        <v>0.8340637904719777</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02310914839348416</v>
+        <v>0.03046196723298688</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5994217004193494</v>
+        <v>0.6233618311850175</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04692796439420401</v>
+        <v>0.01677254449955886</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[[85, 3], [12, 4]]</t>
+          <t>[[86, 2], [12, 3]]</t>
         </is>
       </c>
     </row>
@@ -1464,38 +1464,38 @@
         <v>413</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6399121479487127</v>
+        <v>0.6334679265617699</v>
       </c>
       <c r="G5" t="n">
-        <v>0.112613181658576</v>
+        <v>0.102087000587075</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6147329933541463</v>
+        <v>0.6059168435985118</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1043879239746211</v>
+        <v>0.1030921775378575</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5389713740356903</v>
+        <v>0.5308709505864204</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09072148343009774</v>
+        <v>0.08342079760733727</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6888716623735638</v>
+        <v>0.6839293320000419</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09441974917862796</v>
+        <v>0.08629305498337621</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6838419000393842</v>
+        <v>0.6976243620814944</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1309245608090189</v>
+        <v>0.1207524144196514</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[[58, 30], [6, 8]]</t>
+          <t>[[57, 31], [7, 8]]</t>
         </is>
       </c>
     </row>
@@ -1522,38 +1522,38 @@
         <v>413</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8845286009353255</v>
+        <v>0.8917652478461167</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02473262070158801</v>
+        <v>0.02368923234139502</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6232510583985303</v>
+        <v>0.6393224869699589</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06319775656895868</v>
+        <v>0.07183191611233676</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6549535754871623</v>
+        <v>0.675311833485491</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0776597546568509</v>
+        <v>0.08120354419995369</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8547512305951026</v>
+        <v>0.86400204988922</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03886641593166097</v>
+        <v>0.03645032058253132</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8122289202207986</v>
+        <v>0.8261784477328566</v>
       </c>
       <c r="O6" t="n">
-        <v>0.07345399810372691</v>
+        <v>0.07749796082853239</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[[88, 1], [11, 4]]</t>
+          <t>[[88, 0], [11, 4]]</t>
         </is>
       </c>
     </row>
